--- a/grille_evaluation_CR.xlsx
+++ b/grille_evaluation_CR.xlsx
@@ -281,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -441,6 +441,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1060,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1871,27 +1889,27 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Forme</t>
+          <t xml:space="preserve">  5. Rédaction</t>
         </is>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Terminologie</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Vérifier que le vocabulaire radiothérapeutique est correct et standardisé en français : termes de fractionnement, dosimétrie, volumes (GTV, CTV, PTV), techniques.</t>
         </is>
@@ -1930,7 +1948,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Lisibilité &amp; style</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
@@ -1940,7 +1958,7 @@
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>Évaluer si le texte est fluide, naturel et adapté au style d'un compte rendu médical français : ton professionnel, phrases bien construites, absence de répétitions maladroites.</t>
+          <t>Évaluer si le CR suit une structure logique et claire : contexte clinique → diagnostic → traitement → tolérance → bilan → suivi. Les informations doivent être dans un ordre cohérent.</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -1977,7 +1995,7 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Synthèse &amp; Lisibilité</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
@@ -1987,137 +2005,131 @@
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>Évaluer si le CR suit une structure logique et claire : contexte clinique → diagnostic → traitement → tolérance → bilan → suivi. Les informations doivent être dans un ordre cohérent.</t>
+          <t>Évaluer si le texte est fluide, naturel et adapté au style d'un CR médical, et si le CR est concis et va à l'essentiel : absence de répétitions, style professionnel, lisibilité générale.</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>Structure absente ou chaotique, informations mélangées sans logique.</t>
+          <t>Texte illisible ou clairement non médical, avec répétitions majeures.</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>Structure partielle, plusieurs sections dans le désordre.</t>
+          <t>Texte compréhensible mais avec des maladresses stylistiques ou répétitions notables.</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Structure globalement logique avec quelques éléments mal positionnés.</t>
+          <t>Texte globalement fluide avec quelques légères imperfections de style ou concision.</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>Structure claire et logique respectant l'ordre attendu d'un CR de radiothérapie.</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Texte naturel, fluide, parfaitement adapté au style d'un CR médical, concis et sans répétition.</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>Synthèse</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Évaluer si le CR est concis et va à l'essentiel : absence de répétitions inutiles, d'informations non pertinentes ou de longueurs excessives.</t>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Correspondance profil → CR</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>⚠ Nécessite le profil patient (seed) sous les yeux. Vérifier que les informations clés du CR (stade, chirurgie, ER/PR, chimiothérapie, âge…) correspondent au profil patient fourni comme données d'entrée.
+⚠ Note : le profil peut être reformulé (pas repris mot pour mot) dans le CR — cela est considéré comme correct.</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>CR très verbeux avec de nombreuses répétitions ou informations hors sujet.</t>
+          <t>Le CR contient des informations qui contredisent directement le profil patient (stade différent, chirurgie incorrecte…).</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Quelques répétitions ou longueurs notables affectant la lisibilité.</t>
+          <t>Plusieurs informations du CR ne correspondent pas au profil patient.</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>CR globalement concis avec quelques redondances mineures.</t>
+          <t>Le CR correspond globalement au profil patient avec une légère divergence mineure.</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>CR parfaitement concis, pertinent, sans répétition ni information superflue.</t>
+          <t>Le CR reflète fidèlement toutes les informations clés du profil patient.</t>
         </is>
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Profil patient non disponible pour cette évaluation.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Correspondance profil → CR</t>
+          <t xml:space="preserve">  6. Cohérence &amp; Impression</t>
         </is>
       </c>
     </row>
     <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Correspondance profil → CR</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>⚠ Nécessite le profil patient (seed) sous les yeux. Vérifier que les informations clés du CR (stade, chirurgie, ER/PR, chimiothérapie, âge…) correspondent au profil patient fourni comme données d'entrée.
-⚠ Note : le profil peut être reformulé (pas repris mot pour mot) dans le CR — cela est considéré comme correct.</t>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Impression globale</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>Quelle est votre impression globale ? Ce CR est-il acceptable pour une utilisation clinique réelle ? Prendre en compte l'ensemble des critères évalués.</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>Le CR contient des informations qui contredisent directement le profil patient (stade différent, chirurgie incorrecte…).</t>
+          <t>CR inacceptable : erreurs majeures.</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>Plusieurs informations du CR ne correspondent pas au profil patient.</t>
+          <t>CR nécessitant des corrections importantes.</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Le CR correspond globalement au profil patient avec une légère divergence mineure.</t>
+          <t>CR globalement acceptable avec quelques réserves.</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>Le CR reflète fidèlement toutes les informations clés du profil patient.</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="inlineStr">
-        <is>
-          <t>Profil patient non disponible pour cette évaluation.</t>
-        </is>
-      </c>
-    </row>
+          <t>CR parfaitement acceptable et prêt pour une utilisation clinique.</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:I2"/>
@@ -2257,18 +2269,19 @@
         </is>
       </c>
       <c r="V4" s="34" t="n"/>
-      <c r="W4" s="36" t="inlineStr">
-        <is>
-          <t>5. Forme</t>
-        </is>
-      </c>
+      <c r="W4" s="35" t="inlineStr">
+        <is>
+          <t>5. Rédaction</t>
+        </is>
+      </c>
+      <c r="Z4" s="34" t="n"/>
       <c r="AA4" s="34" t="n"/>
       <c r="AB4" s="35" t="inlineStr">
         <is>
-          <t>6. Correspondance profil → CR</t>
-        </is>
-      </c>
-      <c r="AC4" s="34" t="n"/>
+          <t>6. Cohérence &amp; Impression</t>
+        </is>
+      </c>
+      <c r="AC4" s="57" t="n"/>
       <c r="AD4" s="38" t="inlineStr">
         <is>
           <t>Commentaires
@@ -2365,33 +2378,33 @@
         </is>
       </c>
       <c r="V5" s="34" t="n"/>
-      <c r="W5" s="42" t="inlineStr">
+      <c r="W5" s="41" t="inlineStr">
+        <is>
+          <t>Physicien Médical</t>
+        </is>
+      </c>
+      <c r="X5" s="42" t="inlineStr">
         <is>
           <t>Médecin Radiothérapeute</t>
         </is>
       </c>
-      <c r="X5" s="42" t="inlineStr">
+      <c r="Y5" s="42" t="inlineStr">
         <is>
           <t>Médecin Radiothérapeute</t>
         </is>
       </c>
-      <c r="Y5" s="42" t="inlineStr">
-        <is>
-          <t>Médecin Radiothérapeute</t>
-        </is>
-      </c>
-      <c r="Z5" s="42" t="inlineStr">
-        <is>
-          <t>Médecin Radiothérapeute</t>
-        </is>
-      </c>
+      <c r="Z5" s="58" t="n"/>
       <c r="AA5" s="34" t="n"/>
       <c r="AB5" s="41" t="inlineStr">
         <is>
           <t>Physicien Médical</t>
         </is>
       </c>
-      <c r="AC5" s="34" t="n"/>
+      <c r="AC5" s="57" t="inlineStr">
+        <is>
+          <t>Médecin Radiothérapeute</t>
+        </is>
+      </c>
       <c r="AD5" s="40" t="n"/>
       <c r="AE5" s="40" t="n"/>
     </row>
@@ -2478,33 +2491,33 @@
         </is>
       </c>
       <c r="V6" s="34" t="n"/>
-      <c r="W6" s="44" t="inlineStr">
+      <c r="W6" s="43" t="inlineStr">
         <is>
           <t>Terminologie</t>
         </is>
       </c>
       <c r="X6" s="44" t="inlineStr">
         <is>
-          <t>Lisibilité &amp; style</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="Y6" s="44" t="inlineStr">
         <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="Z6" s="44" t="inlineStr">
-        <is>
-          <t>Synthèse</t>
-        </is>
-      </c>
+          <t>Synthèse &amp; Lisibilité</t>
+        </is>
+      </c>
+      <c r="Z6" s="59" t="n"/>
       <c r="AA6" s="34" t="n"/>
       <c r="AB6" s="43" t="inlineStr">
         <is>
           <t>Correspondance profil → CR</t>
         </is>
       </c>
-      <c r="AC6" s="34" t="n"/>
+      <c r="AC6" s="60" t="inlineStr">
+        <is>
+          <t>Impression globale</t>
+        </is>
+      </c>
       <c r="AD6" s="40" t="n"/>
       <c r="AE6" s="40" t="n"/>
     </row>
@@ -2598,7 +2611,7 @@
         </is>
       </c>
       <c r="V7" s="34" t="n"/>
-      <c r="W7" s="46" t="inlineStr">
+      <c r="W7" s="45" t="inlineStr">
         <is>
           <t>Le vocabulaire radiothérapeutique français est-il correct et standard ?
 (fractionnement, dosimétrie, champs tangentiels…)</t>
@@ -2606,20 +2619,17 @@
       </c>
       <c r="X7" s="46" t="inlineStr">
         <is>
-          <t>Le texte est-il naturel et fluide ? Le style rédactionnel est-il adapté à un compte rendu médical ?</t>
-        </is>
-      </c>
-      <c r="Y7" s="46" t="inlineStr">
-        <is>
           <t>Le CR suit-il une structure logique et claire ? Les informations sont-elles présentées dans un ordre cohérent ?
 (contexte → diagnostic → traitement → suivi)</t>
         </is>
       </c>
-      <c r="Z7" s="46" t="inlineStr">
-        <is>
-          <t>Le CR est-il concis et pertinent ? Évite-t-il les répétitions inutiles et les informations redondantes ?</t>
-        </is>
-      </c>
+      <c r="Y7" s="46" t="inlineStr">
+        <is>
+          <t>Le texte est-il fluide, concis et adapté au style médical ?
+(lisibilité, concision, absence de répétitions)</t>
+        </is>
+      </c>
+      <c r="Z7" s="61" t="n"/>
       <c r="AA7" s="34" t="n"/>
       <c r="AB7" s="45" t="inlineStr">
         <is>
@@ -2628,7 +2638,12 @@
 ⚠ Note : le profil peut être reformulé (pas repris mot pour mot) dans le CR — cela est considéré comme correct.</t>
         </is>
       </c>
-      <c r="AC7" s="34" t="n"/>
+      <c r="AC7" s="62" t="inlineStr">
+        <is>
+          <t>Quelle est votre impression globale ?
+Ce CR est-il acceptable pour une utilisation clinique ?</t>
+        </is>
+      </c>
       <c r="AD7" s="40" t="n"/>
       <c r="AE7" s="40" t="n"/>
     </row>
@@ -2715,7 +2730,7 @@
         </is>
       </c>
       <c r="V8" s="34" t="n"/>
-      <c r="W8" s="49" t="inlineStr">
+      <c r="W8" s="48" t="inlineStr">
         <is>
           <t>1 · 2 · 3 · 4</t>
         </is>
@@ -2730,18 +2745,18 @@
           <t>1 · 2 · 3 · 4</t>
         </is>
       </c>
-      <c r="Z8" s="49" t="inlineStr">
-        <is>
-          <t>1 · 2 · 3 · 4</t>
-        </is>
-      </c>
+      <c r="Z8" s="63" t="n"/>
       <c r="AA8" s="34" t="n"/>
       <c r="AB8" s="48" t="inlineStr">
         <is>
           <t>1 · 2 · 3 · 4 · N/A</t>
         </is>
       </c>
-      <c r="AC8" s="34" t="n"/>
+      <c r="AC8" s="60" t="inlineStr">
+        <is>
+          <t>1 · 2 · 3 · 4</t>
+        </is>
+      </c>
       <c r="AD8" s="47" t="n"/>
       <c r="AE8" s="47" t="n"/>
     </row>
@@ -2776,13 +2791,13 @@
       <c r="T9" s="53" t="inlineStr"/>
       <c r="U9" s="53" t="inlineStr"/>
       <c r="V9" s="34" t="n"/>
-      <c r="W9" s="53" t="inlineStr"/>
-      <c r="X9" s="53" t="inlineStr"/>
-      <c r="Y9" s="53" t="inlineStr"/>
-      <c r="Z9" s="53" t="inlineStr"/>
+      <c r="W9" s="52" t="inlineStr"/>
+      <c r="X9" s="53" t="n"/>
+      <c r="Y9" s="53" t="n"/>
+      <c r="Z9" s="64" t="n"/>
       <c r="AA9" s="34" t="n"/>
       <c r="AB9" s="52" t="inlineStr"/>
-      <c r="AC9" s="34" t="n"/>
+      <c r="AC9" s="62" t="n"/>
       <c r="AD9" s="54" t="inlineStr"/>
       <c r="AE9" s="55" t="inlineStr"/>
     </row>
@@ -2817,13 +2832,13 @@
       <c r="T10" s="53" t="inlineStr"/>
       <c r="U10" s="53" t="inlineStr"/>
       <c r="V10" s="34" t="n"/>
-      <c r="W10" s="53" t="inlineStr"/>
-      <c r="X10" s="53" t="inlineStr"/>
-      <c r="Y10" s="53" t="inlineStr"/>
-      <c r="Z10" s="53" t="inlineStr"/>
+      <c r="W10" s="52" t="inlineStr"/>
+      <c r="X10" s="53" t="n"/>
+      <c r="Y10" s="53" t="n"/>
+      <c r="Z10" s="64" t="n"/>
       <c r="AA10" s="34" t="n"/>
       <c r="AB10" s="52" t="inlineStr"/>
-      <c r="AC10" s="34" t="n"/>
+      <c r="AC10" s="62" t="n"/>
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="55" t="inlineStr"/>
     </row>
@@ -2858,13 +2873,13 @@
       <c r="T11" s="53" t="inlineStr"/>
       <c r="U11" s="53" t="inlineStr"/>
       <c r="V11" s="34" t="n"/>
-      <c r="W11" s="53" t="inlineStr"/>
-      <c r="X11" s="53" t="inlineStr"/>
-      <c r="Y11" s="53" t="inlineStr"/>
-      <c r="Z11" s="53" t="inlineStr"/>
+      <c r="W11" s="52" t="inlineStr"/>
+      <c r="X11" s="53" t="n"/>
+      <c r="Y11" s="53" t="n"/>
+      <c r="Z11" s="64" t="n"/>
       <c r="AA11" s="34" t="n"/>
       <c r="AB11" s="52" t="inlineStr"/>
-      <c r="AC11" s="34" t="n"/>
+      <c r="AC11" s="62" t="n"/>
       <c r="AD11" s="54" t="inlineStr"/>
       <c r="AE11" s="55" t="inlineStr"/>
     </row>
@@ -2899,13 +2914,13 @@
       <c r="T12" s="53" t="inlineStr"/>
       <c r="U12" s="53" t="inlineStr"/>
       <c r="V12" s="34" t="n"/>
-      <c r="W12" s="53" t="inlineStr"/>
-      <c r="X12" s="53" t="inlineStr"/>
-      <c r="Y12" s="53" t="inlineStr"/>
-      <c r="Z12" s="53" t="inlineStr"/>
+      <c r="W12" s="52" t="inlineStr"/>
+      <c r="X12" s="53" t="n"/>
+      <c r="Y12" s="53" t="n"/>
+      <c r="Z12" s="64" t="n"/>
       <c r="AA12" s="34" t="n"/>
       <c r="AB12" s="52" t="inlineStr"/>
-      <c r="AC12" s="34" t="n"/>
+      <c r="AC12" s="62" t="n"/>
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="55" t="inlineStr"/>
     </row>
@@ -2940,13 +2955,13 @@
       <c r="T13" s="53" t="inlineStr"/>
       <c r="U13" s="53" t="inlineStr"/>
       <c r="V13" s="34" t="n"/>
-      <c r="W13" s="53" t="inlineStr"/>
-      <c r="X13" s="53" t="inlineStr"/>
-      <c r="Y13" s="53" t="inlineStr"/>
-      <c r="Z13" s="53" t="inlineStr"/>
+      <c r="W13" s="52" t="inlineStr"/>
+      <c r="X13" s="53" t="n"/>
+      <c r="Y13" s="53" t="n"/>
+      <c r="Z13" s="64" t="n"/>
       <c r="AA13" s="34" t="n"/>
       <c r="AB13" s="52" t="inlineStr"/>
-      <c r="AC13" s="34" t="n"/>
+      <c r="AC13" s="62" t="n"/>
       <c r="AD13" s="54" t="inlineStr"/>
       <c r="AE13" s="55" t="inlineStr"/>
     </row>
@@ -2981,13 +2996,13 @@
       <c r="T14" s="53" t="inlineStr"/>
       <c r="U14" s="53" t="inlineStr"/>
       <c r="V14" s="34" t="n"/>
-      <c r="W14" s="53" t="inlineStr"/>
-      <c r="X14" s="53" t="inlineStr"/>
-      <c r="Y14" s="53" t="inlineStr"/>
-      <c r="Z14" s="53" t="inlineStr"/>
+      <c r="W14" s="52" t="inlineStr"/>
+      <c r="X14" s="53" t="n"/>
+      <c r="Y14" s="53" t="n"/>
+      <c r="Z14" s="64" t="n"/>
       <c r="AA14" s="34" t="n"/>
       <c r="AB14" s="52" t="inlineStr"/>
-      <c r="AC14" s="34" t="n"/>
+      <c r="AC14" s="62" t="n"/>
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="55" t="inlineStr"/>
     </row>
@@ -3022,13 +3037,13 @@
       <c r="T15" s="53" t="inlineStr"/>
       <c r="U15" s="53" t="inlineStr"/>
       <c r="V15" s="34" t="n"/>
-      <c r="W15" s="53" t="inlineStr"/>
-      <c r="X15" s="53" t="inlineStr"/>
-      <c r="Y15" s="53" t="inlineStr"/>
-      <c r="Z15" s="53" t="inlineStr"/>
+      <c r="W15" s="52" t="inlineStr"/>
+      <c r="X15" s="53" t="n"/>
+      <c r="Y15" s="53" t="n"/>
+      <c r="Z15" s="64" t="n"/>
       <c r="AA15" s="34" t="n"/>
       <c r="AB15" s="52" t="inlineStr"/>
-      <c r="AC15" s="34" t="n"/>
+      <c r="AC15" s="62" t="n"/>
       <c r="AD15" s="54" t="inlineStr"/>
       <c r="AE15" s="55" t="inlineStr"/>
     </row>
@@ -3063,13 +3078,13 @@
       <c r="T16" s="53" t="inlineStr"/>
       <c r="U16" s="53" t="inlineStr"/>
       <c r="V16" s="34" t="n"/>
-      <c r="W16" s="53" t="inlineStr"/>
-      <c r="X16" s="53" t="inlineStr"/>
-      <c r="Y16" s="53" t="inlineStr"/>
-      <c r="Z16" s="53" t="inlineStr"/>
+      <c r="W16" s="52" t="inlineStr"/>
+      <c r="X16" s="53" t="n"/>
+      <c r="Y16" s="53" t="n"/>
+      <c r="Z16" s="64" t="n"/>
       <c r="AA16" s="34" t="n"/>
       <c r="AB16" s="52" t="inlineStr"/>
-      <c r="AC16" s="34" t="n"/>
+      <c r="AC16" s="62" t="n"/>
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="55" t="inlineStr"/>
     </row>
@@ -3104,13 +3119,13 @@
       <c r="T17" s="53" t="inlineStr"/>
       <c r="U17" s="53" t="inlineStr"/>
       <c r="V17" s="34" t="n"/>
-      <c r="W17" s="53" t="inlineStr"/>
-      <c r="X17" s="53" t="inlineStr"/>
-      <c r="Y17" s="53" t="inlineStr"/>
-      <c r="Z17" s="53" t="inlineStr"/>
+      <c r="W17" s="52" t="inlineStr"/>
+      <c r="X17" s="53" t="n"/>
+      <c r="Y17" s="53" t="n"/>
+      <c r="Z17" s="64" t="n"/>
       <c r="AA17" s="34" t="n"/>
       <c r="AB17" s="52" t="inlineStr"/>
-      <c r="AC17" s="34" t="n"/>
+      <c r="AC17" s="62" t="n"/>
       <c r="AD17" s="54" t="inlineStr"/>
       <c r="AE17" s="55" t="inlineStr"/>
     </row>
@@ -3145,13 +3160,13 @@
       <c r="T18" s="53" t="inlineStr"/>
       <c r="U18" s="53" t="inlineStr"/>
       <c r="V18" s="34" t="n"/>
-      <c r="W18" s="53" t="inlineStr"/>
-      <c r="X18" s="53" t="inlineStr"/>
-      <c r="Y18" s="53" t="inlineStr"/>
-      <c r="Z18" s="53" t="inlineStr"/>
+      <c r="W18" s="52" t="inlineStr"/>
+      <c r="X18" s="53" t="n"/>
+      <c r="Y18" s="53" t="n"/>
+      <c r="Z18" s="64" t="n"/>
       <c r="AA18" s="34" t="n"/>
       <c r="AB18" s="52" t="inlineStr"/>
-      <c r="AC18" s="34" t="n"/>
+      <c r="AC18" s="62" t="n"/>
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="55" t="inlineStr"/>
     </row>
@@ -3186,13 +3201,13 @@
       <c r="T19" s="53" t="inlineStr"/>
       <c r="U19" s="53" t="inlineStr"/>
       <c r="V19" s="34" t="n"/>
-      <c r="W19" s="53" t="inlineStr"/>
-      <c r="X19" s="53" t="inlineStr"/>
-      <c r="Y19" s="53" t="inlineStr"/>
-      <c r="Z19" s="53" t="inlineStr"/>
+      <c r="W19" s="52" t="inlineStr"/>
+      <c r="X19" s="53" t="n"/>
+      <c r="Y19" s="53" t="n"/>
+      <c r="Z19" s="64" t="n"/>
       <c r="AA19" s="34" t="n"/>
       <c r="AB19" s="52" t="inlineStr"/>
-      <c r="AC19" s="34" t="n"/>
+      <c r="AC19" s="62" t="n"/>
       <c r="AD19" s="54" t="inlineStr"/>
       <c r="AE19" s="55" t="inlineStr"/>
     </row>
@@ -3227,13 +3242,13 @@
       <c r="T20" s="53" t="inlineStr"/>
       <c r="U20" s="53" t="inlineStr"/>
       <c r="V20" s="34" t="n"/>
-      <c r="W20" s="53" t="inlineStr"/>
-      <c r="X20" s="53" t="inlineStr"/>
-      <c r="Y20" s="53" t="inlineStr"/>
-      <c r="Z20" s="53" t="inlineStr"/>
+      <c r="W20" s="52" t="inlineStr"/>
+      <c r="X20" s="53" t="n"/>
+      <c r="Y20" s="53" t="n"/>
+      <c r="Z20" s="64" t="n"/>
       <c r="AA20" s="34" t="n"/>
       <c r="AB20" s="52" t="inlineStr"/>
-      <c r="AC20" s="34" t="n"/>
+      <c r="AC20" s="62" t="n"/>
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="55" t="inlineStr"/>
     </row>
@@ -3268,13 +3283,13 @@
       <c r="T21" s="53" t="inlineStr"/>
       <c r="U21" s="53" t="inlineStr"/>
       <c r="V21" s="34" t="n"/>
-      <c r="W21" s="53" t="inlineStr"/>
-      <c r="X21" s="53" t="inlineStr"/>
-      <c r="Y21" s="53" t="inlineStr"/>
-      <c r="Z21" s="53" t="inlineStr"/>
+      <c r="W21" s="52" t="inlineStr"/>
+      <c r="X21" s="53" t="n"/>
+      <c r="Y21" s="53" t="n"/>
+      <c r="Z21" s="64" t="n"/>
       <c r="AA21" s="34" t="n"/>
       <c r="AB21" s="52" t="inlineStr"/>
-      <c r="AC21" s="34" t="n"/>
+      <c r="AC21" s="62" t="n"/>
       <c r="AD21" s="54" t="inlineStr"/>
       <c r="AE21" s="55" t="inlineStr"/>
     </row>
@@ -3309,13 +3324,13 @@
       <c r="T22" s="53" t="inlineStr"/>
       <c r="U22" s="53" t="inlineStr"/>
       <c r="V22" s="34" t="n"/>
-      <c r="W22" s="53" t="inlineStr"/>
-      <c r="X22" s="53" t="inlineStr"/>
-      <c r="Y22" s="53" t="inlineStr"/>
-      <c r="Z22" s="53" t="inlineStr"/>
+      <c r="W22" s="52" t="inlineStr"/>
+      <c r="X22" s="53" t="n"/>
+      <c r="Y22" s="53" t="n"/>
+      <c r="Z22" s="64" t="n"/>
       <c r="AA22" s="34" t="n"/>
       <c r="AB22" s="52" t="inlineStr"/>
-      <c r="AC22" s="34" t="n"/>
+      <c r="AC22" s="62" t="n"/>
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="55" t="inlineStr"/>
     </row>
@@ -3350,13 +3365,13 @@
       <c r="T23" s="53" t="inlineStr"/>
       <c r="U23" s="53" t="inlineStr"/>
       <c r="V23" s="34" t="n"/>
-      <c r="W23" s="53" t="inlineStr"/>
-      <c r="X23" s="53" t="inlineStr"/>
-      <c r="Y23" s="53" t="inlineStr"/>
-      <c r="Z23" s="53" t="inlineStr"/>
+      <c r="W23" s="52" t="inlineStr"/>
+      <c r="X23" s="53" t="n"/>
+      <c r="Y23" s="53" t="n"/>
+      <c r="Z23" s="64" t="n"/>
       <c r="AA23" s="34" t="n"/>
       <c r="AB23" s="52" t="inlineStr"/>
-      <c r="AC23" s="34" t="n"/>
+      <c r="AC23" s="62" t="n"/>
       <c r="AD23" s="54" t="inlineStr"/>
       <c r="AE23" s="55" t="inlineStr"/>
     </row>
@@ -3391,13 +3406,13 @@
       <c r="T24" s="53" t="inlineStr"/>
       <c r="U24" s="53" t="inlineStr"/>
       <c r="V24" s="34" t="n"/>
-      <c r="W24" s="53" t="inlineStr"/>
-      <c r="X24" s="53" t="inlineStr"/>
-      <c r="Y24" s="53" t="inlineStr"/>
-      <c r="Z24" s="53" t="inlineStr"/>
+      <c r="W24" s="52" t="inlineStr"/>
+      <c r="X24" s="53" t="n"/>
+      <c r="Y24" s="53" t="n"/>
+      <c r="Z24" s="64" t="n"/>
       <c r="AA24" s="34" t="n"/>
       <c r="AB24" s="52" t="inlineStr"/>
-      <c r="AC24" s="34" t="n"/>
+      <c r="AC24" s="62" t="n"/>
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="55" t="inlineStr"/>
     </row>
@@ -3432,13 +3447,13 @@
       <c r="T25" s="53" t="inlineStr"/>
       <c r="U25" s="53" t="inlineStr"/>
       <c r="V25" s="34" t="n"/>
-      <c r="W25" s="53" t="inlineStr"/>
-      <c r="X25" s="53" t="inlineStr"/>
-      <c r="Y25" s="53" t="inlineStr"/>
-      <c r="Z25" s="53" t="inlineStr"/>
+      <c r="W25" s="52" t="inlineStr"/>
+      <c r="X25" s="53" t="n"/>
+      <c r="Y25" s="53" t="n"/>
+      <c r="Z25" s="64" t="n"/>
       <c r="AA25" s="34" t="n"/>
       <c r="AB25" s="52" t="inlineStr"/>
-      <c r="AC25" s="34" t="n"/>
+      <c r="AC25" s="62" t="n"/>
       <c r="AD25" s="54" t="inlineStr"/>
       <c r="AE25" s="55" t="inlineStr"/>
     </row>
@@ -3473,13 +3488,13 @@
       <c r="T26" s="53" t="inlineStr"/>
       <c r="U26" s="53" t="inlineStr"/>
       <c r="V26" s="34" t="n"/>
-      <c r="W26" s="53" t="inlineStr"/>
-      <c r="X26" s="53" t="inlineStr"/>
-      <c r="Y26" s="53" t="inlineStr"/>
-      <c r="Z26" s="53" t="inlineStr"/>
+      <c r="W26" s="52" t="inlineStr"/>
+      <c r="X26" s="53" t="n"/>
+      <c r="Y26" s="53" t="n"/>
+      <c r="Z26" s="64" t="n"/>
       <c r="AA26" s="34" t="n"/>
       <c r="AB26" s="52" t="inlineStr"/>
-      <c r="AC26" s="34" t="n"/>
+      <c r="AC26" s="62" t="n"/>
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="55" t="inlineStr"/>
     </row>
@@ -3514,13 +3529,13 @@
       <c r="T27" s="53" t="inlineStr"/>
       <c r="U27" s="53" t="inlineStr"/>
       <c r="V27" s="34" t="n"/>
-      <c r="W27" s="53" t="inlineStr"/>
-      <c r="X27" s="53" t="inlineStr"/>
-      <c r="Y27" s="53" t="inlineStr"/>
-      <c r="Z27" s="53" t="inlineStr"/>
+      <c r="W27" s="52" t="inlineStr"/>
+      <c r="X27" s="53" t="n"/>
+      <c r="Y27" s="53" t="n"/>
+      <c r="Z27" s="64" t="n"/>
       <c r="AA27" s="34" t="n"/>
       <c r="AB27" s="52" t="inlineStr"/>
-      <c r="AC27" s="34" t="n"/>
+      <c r="AC27" s="62" t="n"/>
       <c r="AD27" s="54" t="inlineStr"/>
       <c r="AE27" s="55" t="inlineStr"/>
     </row>
@@ -3555,13 +3570,13 @@
       <c r="T28" s="53" t="inlineStr"/>
       <c r="U28" s="53" t="inlineStr"/>
       <c r="V28" s="34" t="n"/>
-      <c r="W28" s="53" t="inlineStr"/>
-      <c r="X28" s="53" t="inlineStr"/>
-      <c r="Y28" s="53" t="inlineStr"/>
-      <c r="Z28" s="53" t="inlineStr"/>
+      <c r="W28" s="52" t="inlineStr"/>
+      <c r="X28" s="53" t="n"/>
+      <c r="Y28" s="53" t="n"/>
+      <c r="Z28" s="64" t="n"/>
       <c r="AA28" s="34" t="n"/>
       <c r="AB28" s="52" t="inlineStr"/>
-      <c r="AC28" s="34" t="n"/>
+      <c r="AC28" s="62" t="n"/>
       <c r="AD28" s="54" t="inlineStr"/>
       <c r="AE28" s="55" t="inlineStr"/>
     </row>
@@ -3596,13 +3611,13 @@
       <c r="T29" s="53" t="inlineStr"/>
       <c r="U29" s="53" t="inlineStr"/>
       <c r="V29" s="34" t="n"/>
-      <c r="W29" s="53" t="inlineStr"/>
-      <c r="X29" s="53" t="inlineStr"/>
-      <c r="Y29" s="53" t="inlineStr"/>
-      <c r="Z29" s="53" t="inlineStr"/>
+      <c r="W29" s="52" t="inlineStr"/>
+      <c r="X29" s="53" t="n"/>
+      <c r="Y29" s="53" t="n"/>
+      <c r="Z29" s="64" t="n"/>
       <c r="AA29" s="34" t="n"/>
       <c r="AB29" s="52" t="inlineStr"/>
-      <c r="AC29" s="34" t="n"/>
+      <c r="AC29" s="62" t="n"/>
       <c r="AD29" s="54" t="inlineStr"/>
       <c r="AE29" s="55" t="inlineStr"/>
     </row>
@@ -3637,13 +3652,13 @@
       <c r="T30" s="53" t="inlineStr"/>
       <c r="U30" s="53" t="inlineStr"/>
       <c r="V30" s="34" t="n"/>
-      <c r="W30" s="53" t="inlineStr"/>
-      <c r="X30" s="53" t="inlineStr"/>
-      <c r="Y30" s="53" t="inlineStr"/>
-      <c r="Z30" s="53" t="inlineStr"/>
+      <c r="W30" s="52" t="inlineStr"/>
+      <c r="X30" s="53" t="n"/>
+      <c r="Y30" s="53" t="n"/>
+      <c r="Z30" s="64" t="n"/>
       <c r="AA30" s="34" t="n"/>
       <c r="AB30" s="52" t="inlineStr"/>
-      <c r="AC30" s="34" t="n"/>
+      <c r="AC30" s="62" t="n"/>
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="55" t="inlineStr"/>
     </row>
@@ -3678,13 +3693,13 @@
       <c r="T31" s="53" t="inlineStr"/>
       <c r="U31" s="53" t="inlineStr"/>
       <c r="V31" s="34" t="n"/>
-      <c r="W31" s="53" t="inlineStr"/>
-      <c r="X31" s="53" t="inlineStr"/>
-      <c r="Y31" s="53" t="inlineStr"/>
-      <c r="Z31" s="53" t="inlineStr"/>
+      <c r="W31" s="52" t="inlineStr"/>
+      <c r="X31" s="53" t="n"/>
+      <c r="Y31" s="53" t="n"/>
+      <c r="Z31" s="64" t="n"/>
       <c r="AA31" s="34" t="n"/>
       <c r="AB31" s="52" t="inlineStr"/>
-      <c r="AC31" s="34" t="n"/>
+      <c r="AC31" s="62" t="n"/>
       <c r="AD31" s="54" t="inlineStr"/>
       <c r="AE31" s="55" t="inlineStr"/>
     </row>
@@ -3719,13 +3734,13 @@
       <c r="T32" s="53" t="inlineStr"/>
       <c r="U32" s="53" t="inlineStr"/>
       <c r="V32" s="34" t="n"/>
-      <c r="W32" s="53" t="inlineStr"/>
-      <c r="X32" s="53" t="inlineStr"/>
-      <c r="Y32" s="53" t="inlineStr"/>
-      <c r="Z32" s="53" t="inlineStr"/>
+      <c r="W32" s="52" t="inlineStr"/>
+      <c r="X32" s="53" t="n"/>
+      <c r="Y32" s="53" t="n"/>
+      <c r="Z32" s="64" t="n"/>
       <c r="AA32" s="34" t="n"/>
       <c r="AB32" s="52" t="inlineStr"/>
-      <c r="AC32" s="34" t="n"/>
+      <c r="AC32" s="62" t="n"/>
       <c r="AD32" s="54" t="inlineStr"/>
       <c r="AE32" s="55" t="inlineStr"/>
     </row>
@@ -3760,13 +3775,13 @@
       <c r="T33" s="53" t="inlineStr"/>
       <c r="U33" s="53" t="inlineStr"/>
       <c r="V33" s="34" t="n"/>
-      <c r="W33" s="53" t="inlineStr"/>
-      <c r="X33" s="53" t="inlineStr"/>
-      <c r="Y33" s="53" t="inlineStr"/>
-      <c r="Z33" s="53" t="inlineStr"/>
+      <c r="W33" s="52" t="inlineStr"/>
+      <c r="X33" s="53" t="n"/>
+      <c r="Y33" s="53" t="n"/>
+      <c r="Z33" s="64" t="n"/>
       <c r="AA33" s="34" t="n"/>
       <c r="AB33" s="52" t="inlineStr"/>
-      <c r="AC33" s="34" t="n"/>
+      <c r="AC33" s="62" t="n"/>
       <c r="AD33" s="54" t="inlineStr"/>
       <c r="AE33" s="55" t="inlineStr"/>
     </row>
@@ -3801,13 +3816,13 @@
       <c r="T34" s="53" t="inlineStr"/>
       <c r="U34" s="53" t="inlineStr"/>
       <c r="V34" s="34" t="n"/>
-      <c r="W34" s="53" t="inlineStr"/>
-      <c r="X34" s="53" t="inlineStr"/>
-      <c r="Y34" s="53" t="inlineStr"/>
-      <c r="Z34" s="53" t="inlineStr"/>
+      <c r="W34" s="52" t="inlineStr"/>
+      <c r="X34" s="53" t="n"/>
+      <c r="Y34" s="53" t="n"/>
+      <c r="Z34" s="64" t="n"/>
       <c r="AA34" s="34" t="n"/>
       <c r="AB34" s="52" t="inlineStr"/>
-      <c r="AC34" s="34" t="n"/>
+      <c r="AC34" s="62" t="n"/>
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="55" t="inlineStr"/>
     </row>
@@ -3842,13 +3857,13 @@
       <c r="T35" s="53" t="inlineStr"/>
       <c r="U35" s="53" t="inlineStr"/>
       <c r="V35" s="34" t="n"/>
-      <c r="W35" s="53" t="inlineStr"/>
-      <c r="X35" s="53" t="inlineStr"/>
-      <c r="Y35" s="53" t="inlineStr"/>
-      <c r="Z35" s="53" t="inlineStr"/>
+      <c r="W35" s="52" t="inlineStr"/>
+      <c r="X35" s="53" t="n"/>
+      <c r="Y35" s="53" t="n"/>
+      <c r="Z35" s="64" t="n"/>
       <c r="AA35" s="34" t="n"/>
       <c r="AB35" s="52" t="inlineStr"/>
-      <c r="AC35" s="34" t="n"/>
+      <c r="AC35" s="62" t="n"/>
       <c r="AD35" s="54" t="inlineStr"/>
       <c r="AE35" s="55" t="inlineStr"/>
     </row>
@@ -3883,13 +3898,13 @@
       <c r="T36" s="53" t="inlineStr"/>
       <c r="U36" s="53" t="inlineStr"/>
       <c r="V36" s="34" t="n"/>
-      <c r="W36" s="53" t="inlineStr"/>
-      <c r="X36" s="53" t="inlineStr"/>
-      <c r="Y36" s="53" t="inlineStr"/>
-      <c r="Z36" s="53" t="inlineStr"/>
+      <c r="W36" s="52" t="inlineStr"/>
+      <c r="X36" s="53" t="n"/>
+      <c r="Y36" s="53" t="n"/>
+      <c r="Z36" s="64" t="n"/>
       <c r="AA36" s="34" t="n"/>
       <c r="AB36" s="52" t="inlineStr"/>
-      <c r="AC36" s="34" t="n"/>
+      <c r="AC36" s="62" t="n"/>
       <c r="AD36" s="54" t="inlineStr"/>
       <c r="AE36" s="55" t="inlineStr"/>
     </row>
@@ -3924,13 +3939,13 @@
       <c r="T37" s="53" t="inlineStr"/>
       <c r="U37" s="53" t="inlineStr"/>
       <c r="V37" s="34" t="n"/>
-      <c r="W37" s="53" t="inlineStr"/>
-      <c r="X37" s="53" t="inlineStr"/>
-      <c r="Y37" s="53" t="inlineStr"/>
-      <c r="Z37" s="53" t="inlineStr"/>
+      <c r="W37" s="52" t="inlineStr"/>
+      <c r="X37" s="53" t="n"/>
+      <c r="Y37" s="53" t="n"/>
+      <c r="Z37" s="64" t="n"/>
       <c r="AA37" s="34" t="n"/>
       <c r="AB37" s="52" t="inlineStr"/>
-      <c r="AC37" s="34" t="n"/>
+      <c r="AC37" s="62" t="n"/>
       <c r="AD37" s="54" t="inlineStr"/>
       <c r="AE37" s="55" t="inlineStr"/>
     </row>
@@ -3965,13 +3980,13 @@
       <c r="T38" s="53" t="inlineStr"/>
       <c r="U38" s="53" t="inlineStr"/>
       <c r="V38" s="34" t="n"/>
-      <c r="W38" s="53" t="inlineStr"/>
-      <c r="X38" s="53" t="inlineStr"/>
-      <c r="Y38" s="53" t="inlineStr"/>
-      <c r="Z38" s="53" t="inlineStr"/>
+      <c r="W38" s="52" t="inlineStr"/>
+      <c r="X38" s="53" t="n"/>
+      <c r="Y38" s="53" t="n"/>
+      <c r="Z38" s="64" t="n"/>
       <c r="AA38" s="34" t="n"/>
       <c r="AB38" s="52" t="inlineStr"/>
-      <c r="AC38" s="34" t="n"/>
+      <c r="AC38" s="62" t="n"/>
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="55" t="inlineStr"/>
     </row>
@@ -4006,13 +4021,13 @@
       <c r="T39" s="53" t="inlineStr"/>
       <c r="U39" s="53" t="inlineStr"/>
       <c r="V39" s="34" t="n"/>
-      <c r="W39" s="53" t="inlineStr"/>
-      <c r="X39" s="53" t="inlineStr"/>
-      <c r="Y39" s="53" t="inlineStr"/>
-      <c r="Z39" s="53" t="inlineStr"/>
+      <c r="W39" s="52" t="inlineStr"/>
+      <c r="X39" s="53" t="n"/>
+      <c r="Y39" s="53" t="n"/>
+      <c r="Z39" s="64" t="n"/>
       <c r="AA39" s="34" t="n"/>
       <c r="AB39" s="52" t="inlineStr"/>
-      <c r="AC39" s="34" t="n"/>
+      <c r="AC39" s="62" t="n"/>
       <c r="AD39" s="54" t="inlineStr"/>
       <c r="AE39" s="55" t="inlineStr"/>
     </row>
@@ -4047,13 +4062,13 @@
       <c r="T40" s="53" t="inlineStr"/>
       <c r="U40" s="53" t="inlineStr"/>
       <c r="V40" s="34" t="n"/>
-      <c r="W40" s="53" t="inlineStr"/>
-      <c r="X40" s="53" t="inlineStr"/>
-      <c r="Y40" s="53" t="inlineStr"/>
-      <c r="Z40" s="53" t="inlineStr"/>
+      <c r="W40" s="52" t="inlineStr"/>
+      <c r="X40" s="53" t="n"/>
+      <c r="Y40" s="53" t="n"/>
+      <c r="Z40" s="64" t="n"/>
       <c r="AA40" s="34" t="n"/>
       <c r="AB40" s="52" t="inlineStr"/>
-      <c r="AC40" s="34" t="n"/>
+      <c r="AC40" s="62" t="n"/>
       <c r="AD40" s="54" t="inlineStr"/>
       <c r="AE40" s="55" t="inlineStr"/>
     </row>
@@ -4088,13 +4103,13 @@
       <c r="T41" s="53" t="inlineStr"/>
       <c r="U41" s="53" t="inlineStr"/>
       <c r="V41" s="34" t="n"/>
-      <c r="W41" s="53" t="inlineStr"/>
-      <c r="X41" s="53" t="inlineStr"/>
-      <c r="Y41" s="53" t="inlineStr"/>
-      <c r="Z41" s="53" t="inlineStr"/>
+      <c r="W41" s="52" t="inlineStr"/>
+      <c r="X41" s="53" t="n"/>
+      <c r="Y41" s="53" t="n"/>
+      <c r="Z41" s="64" t="n"/>
       <c r="AA41" s="34" t="n"/>
       <c r="AB41" s="52" t="inlineStr"/>
-      <c r="AC41" s="34" t="n"/>
+      <c r="AC41" s="62" t="n"/>
       <c r="AD41" s="54" t="inlineStr"/>
       <c r="AE41" s="55" t="inlineStr"/>
     </row>
@@ -4129,13 +4144,13 @@
       <c r="T42" s="53" t="inlineStr"/>
       <c r="U42" s="53" t="inlineStr"/>
       <c r="V42" s="34" t="n"/>
-      <c r="W42" s="53" t="inlineStr"/>
-      <c r="X42" s="53" t="inlineStr"/>
-      <c r="Y42" s="53" t="inlineStr"/>
-      <c r="Z42" s="53" t="inlineStr"/>
+      <c r="W42" s="52" t="inlineStr"/>
+      <c r="X42" s="53" t="n"/>
+      <c r="Y42" s="53" t="n"/>
+      <c r="Z42" s="64" t="n"/>
       <c r="AA42" s="34" t="n"/>
       <c r="AB42" s="52" t="inlineStr"/>
-      <c r="AC42" s="34" t="n"/>
+      <c r="AC42" s="62" t="n"/>
       <c r="AD42" s="54" t="inlineStr"/>
       <c r="AE42" s="55" t="inlineStr"/>
     </row>
@@ -4170,13 +4185,13 @@
       <c r="T43" s="53" t="inlineStr"/>
       <c r="U43" s="53" t="inlineStr"/>
       <c r="V43" s="34" t="n"/>
-      <c r="W43" s="53" t="inlineStr"/>
-      <c r="X43" s="53" t="inlineStr"/>
-      <c r="Y43" s="53" t="inlineStr"/>
-      <c r="Z43" s="53" t="inlineStr"/>
+      <c r="W43" s="52" t="inlineStr"/>
+      <c r="X43" s="53" t="n"/>
+      <c r="Y43" s="53" t="n"/>
+      <c r="Z43" s="64" t="n"/>
       <c r="AA43" s="34" t="n"/>
       <c r="AB43" s="52" t="inlineStr"/>
-      <c r="AC43" s="34" t="n"/>
+      <c r="AC43" s="62" t="n"/>
       <c r="AD43" s="54" t="inlineStr"/>
       <c r="AE43" s="55" t="inlineStr"/>
     </row>
@@ -4211,13 +4226,13 @@
       <c r="T44" s="53" t="inlineStr"/>
       <c r="U44" s="53" t="inlineStr"/>
       <c r="V44" s="34" t="n"/>
-      <c r="W44" s="53" t="inlineStr"/>
-      <c r="X44" s="53" t="inlineStr"/>
-      <c r="Y44" s="53" t="inlineStr"/>
-      <c r="Z44" s="53" t="inlineStr"/>
+      <c r="W44" s="52" t="inlineStr"/>
+      <c r="X44" s="53" t="n"/>
+      <c r="Y44" s="53" t="n"/>
+      <c r="Z44" s="64" t="n"/>
       <c r="AA44" s="34" t="n"/>
       <c r="AB44" s="52" t="inlineStr"/>
-      <c r="AC44" s="34" t="n"/>
+      <c r="AC44" s="62" t="n"/>
       <c r="AD44" s="54" t="inlineStr"/>
       <c r="AE44" s="55" t="inlineStr"/>
     </row>
@@ -4252,13 +4267,13 @@
       <c r="T45" s="53" t="inlineStr"/>
       <c r="U45" s="53" t="inlineStr"/>
       <c r="V45" s="34" t="n"/>
-      <c r="W45" s="53" t="inlineStr"/>
-      <c r="X45" s="53" t="inlineStr"/>
-      <c r="Y45" s="53" t="inlineStr"/>
-      <c r="Z45" s="53" t="inlineStr"/>
+      <c r="W45" s="52" t="inlineStr"/>
+      <c r="X45" s="53" t="n"/>
+      <c r="Y45" s="53" t="n"/>
+      <c r="Z45" s="64" t="n"/>
       <c r="AA45" s="34" t="n"/>
       <c r="AB45" s="52" t="inlineStr"/>
-      <c r="AC45" s="34" t="n"/>
+      <c r="AC45" s="62" t="n"/>
       <c r="AD45" s="54" t="inlineStr"/>
       <c r="AE45" s="55" t="inlineStr"/>
     </row>
@@ -4293,13 +4308,13 @@
       <c r="T46" s="53" t="inlineStr"/>
       <c r="U46" s="53" t="inlineStr"/>
       <c r="V46" s="34" t="n"/>
-      <c r="W46" s="53" t="inlineStr"/>
-      <c r="X46" s="53" t="inlineStr"/>
-      <c r="Y46" s="53" t="inlineStr"/>
-      <c r="Z46" s="53" t="inlineStr"/>
+      <c r="W46" s="52" t="inlineStr"/>
+      <c r="X46" s="53" t="n"/>
+      <c r="Y46" s="53" t="n"/>
+      <c r="Z46" s="64" t="n"/>
       <c r="AA46" s="34" t="n"/>
       <c r="AB46" s="52" t="inlineStr"/>
-      <c r="AC46" s="34" t="n"/>
+      <c r="AC46" s="62" t="n"/>
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="55" t="inlineStr"/>
     </row>
@@ -4334,13 +4349,13 @@
       <c r="T47" s="53" t="inlineStr"/>
       <c r="U47" s="53" t="inlineStr"/>
       <c r="V47" s="34" t="n"/>
-      <c r="W47" s="53" t="inlineStr"/>
-      <c r="X47" s="53" t="inlineStr"/>
-      <c r="Y47" s="53" t="inlineStr"/>
-      <c r="Z47" s="53" t="inlineStr"/>
+      <c r="W47" s="52" t="inlineStr"/>
+      <c r="X47" s="53" t="n"/>
+      <c r="Y47" s="53" t="n"/>
+      <c r="Z47" s="64" t="n"/>
       <c r="AA47" s="34" t="n"/>
       <c r="AB47" s="52" t="inlineStr"/>
-      <c r="AC47" s="34" t="n"/>
+      <c r="AC47" s="62" t="n"/>
       <c r="AD47" s="54" t="inlineStr"/>
       <c r="AE47" s="55" t="inlineStr"/>
     </row>
@@ -4375,13 +4390,13 @@
       <c r="T48" s="53" t="inlineStr"/>
       <c r="U48" s="53" t="inlineStr"/>
       <c r="V48" s="34" t="n"/>
-      <c r="W48" s="53" t="inlineStr"/>
-      <c r="X48" s="53" t="inlineStr"/>
-      <c r="Y48" s="53" t="inlineStr"/>
-      <c r="Z48" s="53" t="inlineStr"/>
+      <c r="W48" s="52" t="inlineStr"/>
+      <c r="X48" s="53" t="n"/>
+      <c r="Y48" s="53" t="n"/>
+      <c r="Z48" s="64" t="n"/>
       <c r="AA48" s="34" t="n"/>
       <c r="AB48" s="52" t="inlineStr"/>
-      <c r="AC48" s="34" t="n"/>
+      <c r="AC48" s="62" t="n"/>
       <c r="AD48" s="54" t="inlineStr"/>
       <c r="AE48" s="55" t="inlineStr"/>
     </row>
@@ -4416,13 +4431,13 @@
       <c r="T49" s="53" t="inlineStr"/>
       <c r="U49" s="53" t="inlineStr"/>
       <c r="V49" s="34" t="n"/>
-      <c r="W49" s="53" t="inlineStr"/>
-      <c r="X49" s="53" t="inlineStr"/>
-      <c r="Y49" s="53" t="inlineStr"/>
-      <c r="Z49" s="53" t="inlineStr"/>
+      <c r="W49" s="52" t="inlineStr"/>
+      <c r="X49" s="53" t="n"/>
+      <c r="Y49" s="53" t="n"/>
+      <c r="Z49" s="64" t="n"/>
       <c r="AA49" s="34" t="n"/>
       <c r="AB49" s="52" t="inlineStr"/>
-      <c r="AC49" s="34" t="n"/>
+      <c r="AC49" s="62" t="n"/>
       <c r="AD49" s="54" t="inlineStr"/>
       <c r="AE49" s="55" t="inlineStr"/>
     </row>
@@ -4457,13 +4472,13 @@
       <c r="T50" s="53" t="inlineStr"/>
       <c r="U50" s="53" t="inlineStr"/>
       <c r="V50" s="34" t="n"/>
-      <c r="W50" s="53" t="inlineStr"/>
-      <c r="X50" s="53" t="inlineStr"/>
-      <c r="Y50" s="53" t="inlineStr"/>
-      <c r="Z50" s="53" t="inlineStr"/>
+      <c r="W50" s="52" t="inlineStr"/>
+      <c r="X50" s="53" t="n"/>
+      <c r="Y50" s="53" t="n"/>
+      <c r="Z50" s="64" t="n"/>
       <c r="AA50" s="34" t="n"/>
       <c r="AB50" s="52" t="inlineStr"/>
-      <c r="AC50" s="34" t="n"/>
+      <c r="AC50" s="62" t="n"/>
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="55" t="inlineStr"/>
     </row>
@@ -4498,13 +4513,13 @@
       <c r="T51" s="53" t="inlineStr"/>
       <c r="U51" s="53" t="inlineStr"/>
       <c r="V51" s="34" t="n"/>
-      <c r="W51" s="53" t="inlineStr"/>
-      <c r="X51" s="53" t="inlineStr"/>
-      <c r="Y51" s="53" t="inlineStr"/>
-      <c r="Z51" s="53" t="inlineStr"/>
+      <c r="W51" s="52" t="inlineStr"/>
+      <c r="X51" s="53" t="n"/>
+      <c r="Y51" s="53" t="n"/>
+      <c r="Z51" s="64" t="n"/>
       <c r="AA51" s="34" t="n"/>
       <c r="AB51" s="52" t="inlineStr"/>
-      <c r="AC51" s="34" t="n"/>
+      <c r="AC51" s="62" t="n"/>
       <c r="AD51" s="54" t="inlineStr"/>
       <c r="AE51" s="55" t="inlineStr"/>
     </row>
@@ -4539,13 +4554,13 @@
       <c r="T52" s="53" t="inlineStr"/>
       <c r="U52" s="53" t="inlineStr"/>
       <c r="V52" s="34" t="n"/>
-      <c r="W52" s="53" t="inlineStr"/>
-      <c r="X52" s="53" t="inlineStr"/>
-      <c r="Y52" s="53" t="inlineStr"/>
-      <c r="Z52" s="53" t="inlineStr"/>
+      <c r="W52" s="52" t="inlineStr"/>
+      <c r="X52" s="53" t="n"/>
+      <c r="Y52" s="53" t="n"/>
+      <c r="Z52" s="64" t="n"/>
       <c r="AA52" s="34" t="n"/>
       <c r="AB52" s="52" t="inlineStr"/>
-      <c r="AC52" s="34" t="n"/>
+      <c r="AC52" s="62" t="n"/>
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="55" t="inlineStr"/>
     </row>
@@ -4580,13 +4595,13 @@
       <c r="T53" s="53" t="inlineStr"/>
       <c r="U53" s="53" t="inlineStr"/>
       <c r="V53" s="34" t="n"/>
-      <c r="W53" s="53" t="inlineStr"/>
-      <c r="X53" s="53" t="inlineStr"/>
-      <c r="Y53" s="53" t="inlineStr"/>
-      <c r="Z53" s="53" t="inlineStr"/>
+      <c r="W53" s="52" t="inlineStr"/>
+      <c r="X53" s="53" t="n"/>
+      <c r="Y53" s="53" t="n"/>
+      <c r="Z53" s="64" t="n"/>
       <c r="AA53" s="34" t="n"/>
       <c r="AB53" s="52" t="inlineStr"/>
-      <c r="AC53" s="34" t="n"/>
+      <c r="AC53" s="62" t="n"/>
       <c r="AD53" s="54" t="inlineStr"/>
       <c r="AE53" s="55" t="inlineStr"/>
     </row>
@@ -4621,13 +4636,13 @@
       <c r="T54" s="53" t="inlineStr"/>
       <c r="U54" s="53" t="inlineStr"/>
       <c r="V54" s="34" t="n"/>
-      <c r="W54" s="53" t="inlineStr"/>
-      <c r="X54" s="53" t="inlineStr"/>
-      <c r="Y54" s="53" t="inlineStr"/>
-      <c r="Z54" s="53" t="inlineStr"/>
+      <c r="W54" s="52" t="inlineStr"/>
+      <c r="X54" s="53" t="n"/>
+      <c r="Y54" s="53" t="n"/>
+      <c r="Z54" s="64" t="n"/>
       <c r="AA54" s="34" t="n"/>
       <c r="AB54" s="52" t="inlineStr"/>
-      <c r="AC54" s="34" t="n"/>
+      <c r="AC54" s="62" t="n"/>
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="55" t="inlineStr"/>
     </row>
@@ -4662,13 +4677,13 @@
       <c r="T55" s="53" t="inlineStr"/>
       <c r="U55" s="53" t="inlineStr"/>
       <c r="V55" s="34" t="n"/>
-      <c r="W55" s="53" t="inlineStr"/>
-      <c r="X55" s="53" t="inlineStr"/>
-      <c r="Y55" s="53" t="inlineStr"/>
-      <c r="Z55" s="53" t="inlineStr"/>
+      <c r="W55" s="52" t="inlineStr"/>
+      <c r="X55" s="53" t="n"/>
+      <c r="Y55" s="53" t="n"/>
+      <c r="Z55" s="64" t="n"/>
       <c r="AA55" s="34" t="n"/>
       <c r="AB55" s="52" t="inlineStr"/>
-      <c r="AC55" s="34" t="n"/>
+      <c r="AC55" s="62" t="n"/>
       <c r="AD55" s="54" t="inlineStr"/>
       <c r="AE55" s="55" t="inlineStr"/>
     </row>
@@ -4703,13 +4718,13 @@
       <c r="T56" s="53" t="inlineStr"/>
       <c r="U56" s="53" t="inlineStr"/>
       <c r="V56" s="34" t="n"/>
-      <c r="W56" s="53" t="inlineStr"/>
-      <c r="X56" s="53" t="inlineStr"/>
-      <c r="Y56" s="53" t="inlineStr"/>
-      <c r="Z56" s="53" t="inlineStr"/>
+      <c r="W56" s="52" t="inlineStr"/>
+      <c r="X56" s="53" t="n"/>
+      <c r="Y56" s="53" t="n"/>
+      <c r="Z56" s="64" t="n"/>
       <c r="AA56" s="34" t="n"/>
       <c r="AB56" s="52" t="inlineStr"/>
-      <c r="AC56" s="34" t="n"/>
+      <c r="AC56" s="62" t="n"/>
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="55" t="inlineStr"/>
     </row>
@@ -4744,13 +4759,13 @@
       <c r="T57" s="53" t="inlineStr"/>
       <c r="U57" s="53" t="inlineStr"/>
       <c r="V57" s="34" t="n"/>
-      <c r="W57" s="53" t="inlineStr"/>
-      <c r="X57" s="53" t="inlineStr"/>
-      <c r="Y57" s="53" t="inlineStr"/>
-      <c r="Z57" s="53" t="inlineStr"/>
+      <c r="W57" s="52" t="inlineStr"/>
+      <c r="X57" s="53" t="n"/>
+      <c r="Y57" s="53" t="n"/>
+      <c r="Z57" s="64" t="n"/>
       <c r="AA57" s="34" t="n"/>
       <c r="AB57" s="52" t="inlineStr"/>
-      <c r="AC57" s="34" t="n"/>
+      <c r="AC57" s="62" t="n"/>
       <c r="AD57" s="54" t="inlineStr"/>
       <c r="AE57" s="55" t="inlineStr"/>
     </row>
@@ -4785,13 +4800,13 @@
       <c r="T58" s="53" t="inlineStr"/>
       <c r="U58" s="53" t="inlineStr"/>
       <c r="V58" s="34" t="n"/>
-      <c r="W58" s="53" t="inlineStr"/>
-      <c r="X58" s="53" t="inlineStr"/>
-      <c r="Y58" s="53" t="inlineStr"/>
-      <c r="Z58" s="53" t="inlineStr"/>
+      <c r="W58" s="52" t="inlineStr"/>
+      <c r="X58" s="53" t="n"/>
+      <c r="Y58" s="53" t="n"/>
+      <c r="Z58" s="64" t="n"/>
       <c r="AA58" s="34" t="n"/>
       <c r="AB58" s="52" t="inlineStr"/>
-      <c r="AC58" s="34" t="n"/>
+      <c r="AC58" s="62" t="n"/>
       <c r="AD58" s="54" t="inlineStr"/>
       <c r="AE58" s="55" t="inlineStr"/>
     </row>
@@ -4826,13 +4841,13 @@
       <c r="T59" s="53" t="inlineStr"/>
       <c r="U59" s="53" t="inlineStr"/>
       <c r="V59" s="34" t="n"/>
-      <c r="W59" s="53" t="inlineStr"/>
-      <c r="X59" s="53" t="inlineStr"/>
-      <c r="Y59" s="53" t="inlineStr"/>
-      <c r="Z59" s="53" t="inlineStr"/>
+      <c r="W59" s="52" t="inlineStr"/>
+      <c r="X59" s="53" t="n"/>
+      <c r="Y59" s="53" t="n"/>
+      <c r="Z59" s="64" t="n"/>
       <c r="AA59" s="34" t="n"/>
       <c r="AB59" s="52" t="inlineStr"/>
-      <c r="AC59" s="34" t="n"/>
+      <c r="AC59" s="62" t="n"/>
       <c r="AD59" s="54" t="inlineStr"/>
       <c r="AE59" s="55" t="inlineStr"/>
     </row>
@@ -4867,13 +4882,13 @@
       <c r="T60" s="53" t="inlineStr"/>
       <c r="U60" s="53" t="inlineStr"/>
       <c r="V60" s="34" t="n"/>
-      <c r="W60" s="53" t="inlineStr"/>
-      <c r="X60" s="53" t="inlineStr"/>
-      <c r="Y60" s="53" t="inlineStr"/>
-      <c r="Z60" s="53" t="inlineStr"/>
+      <c r="W60" s="52" t="inlineStr"/>
+      <c r="X60" s="53" t="n"/>
+      <c r="Y60" s="53" t="n"/>
+      <c r="Z60" s="64" t="n"/>
       <c r="AA60" s="34" t="n"/>
       <c r="AB60" s="52" t="inlineStr"/>
-      <c r="AC60" s="34" t="n"/>
+      <c r="AC60" s="62" t="n"/>
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="55" t="inlineStr"/>
     </row>
@@ -4908,13 +4923,13 @@
       <c r="T61" s="53" t="inlineStr"/>
       <c r="U61" s="53" t="inlineStr"/>
       <c r="V61" s="34" t="n"/>
-      <c r="W61" s="53" t="inlineStr"/>
-      <c r="X61" s="53" t="inlineStr"/>
-      <c r="Y61" s="53" t="inlineStr"/>
-      <c r="Z61" s="53" t="inlineStr"/>
+      <c r="W61" s="52" t="inlineStr"/>
+      <c r="X61" s="53" t="n"/>
+      <c r="Y61" s="53" t="n"/>
+      <c r="Z61" s="64" t="n"/>
       <c r="AA61" s="34" t="n"/>
       <c r="AB61" s="52" t="inlineStr"/>
-      <c r="AC61" s="34" t="n"/>
+      <c r="AC61" s="62" t="n"/>
       <c r="AD61" s="54" t="inlineStr"/>
       <c r="AE61" s="55" t="inlineStr"/>
     </row>
@@ -4949,13 +4964,13 @@
       <c r="T62" s="53" t="inlineStr"/>
       <c r="U62" s="53" t="inlineStr"/>
       <c r="V62" s="34" t="n"/>
-      <c r="W62" s="53" t="inlineStr"/>
-      <c r="X62" s="53" t="inlineStr"/>
-      <c r="Y62" s="53" t="inlineStr"/>
-      <c r="Z62" s="53" t="inlineStr"/>
+      <c r="W62" s="52" t="inlineStr"/>
+      <c r="X62" s="53" t="n"/>
+      <c r="Y62" s="53" t="n"/>
+      <c r="Z62" s="64" t="n"/>
       <c r="AA62" s="34" t="n"/>
       <c r="AB62" s="52" t="inlineStr"/>
-      <c r="AC62" s="34" t="n"/>
+      <c r="AC62" s="62" t="n"/>
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="55" t="inlineStr"/>
     </row>
@@ -4990,13 +5005,13 @@
       <c r="T63" s="53" t="inlineStr"/>
       <c r="U63" s="53" t="inlineStr"/>
       <c r="V63" s="34" t="n"/>
-      <c r="W63" s="53" t="inlineStr"/>
-      <c r="X63" s="53" t="inlineStr"/>
-      <c r="Y63" s="53" t="inlineStr"/>
-      <c r="Z63" s="53" t="inlineStr"/>
+      <c r="W63" s="52" t="inlineStr"/>
+      <c r="X63" s="53" t="n"/>
+      <c r="Y63" s="53" t="n"/>
+      <c r="Z63" s="64" t="n"/>
       <c r="AA63" s="34" t="n"/>
       <c r="AB63" s="52" t="inlineStr"/>
-      <c r="AC63" s="34" t="n"/>
+      <c r="AC63" s="62" t="n"/>
       <c r="AD63" s="54" t="inlineStr"/>
       <c r="AE63" s="55" t="inlineStr"/>
     </row>
@@ -5031,13 +5046,13 @@
       <c r="T64" s="53" t="inlineStr"/>
       <c r="U64" s="53" t="inlineStr"/>
       <c r="V64" s="34" t="n"/>
-      <c r="W64" s="53" t="inlineStr"/>
-      <c r="X64" s="53" t="inlineStr"/>
-      <c r="Y64" s="53" t="inlineStr"/>
-      <c r="Z64" s="53" t="inlineStr"/>
+      <c r="W64" s="52" t="inlineStr"/>
+      <c r="X64" s="53" t="n"/>
+      <c r="Y64" s="53" t="n"/>
+      <c r="Z64" s="64" t="n"/>
       <c r="AA64" s="34" t="n"/>
       <c r="AB64" s="52" t="inlineStr"/>
-      <c r="AC64" s="34" t="n"/>
+      <c r="AC64" s="62" t="n"/>
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="55" t="inlineStr"/>
     </row>
@@ -5072,13 +5087,13 @@
       <c r="T65" s="53" t="inlineStr"/>
       <c r="U65" s="53" t="inlineStr"/>
       <c r="V65" s="34" t="n"/>
-      <c r="W65" s="53" t="inlineStr"/>
-      <c r="X65" s="53" t="inlineStr"/>
-      <c r="Y65" s="53" t="inlineStr"/>
-      <c r="Z65" s="53" t="inlineStr"/>
+      <c r="W65" s="52" t="inlineStr"/>
+      <c r="X65" s="53" t="n"/>
+      <c r="Y65" s="53" t="n"/>
+      <c r="Z65" s="64" t="n"/>
       <c r="AA65" s="34" t="n"/>
       <c r="AB65" s="52" t="inlineStr"/>
-      <c r="AC65" s="34" t="n"/>
+      <c r="AC65" s="62" t="n"/>
       <c r="AD65" s="54" t="inlineStr"/>
       <c r="AE65" s="55" t="inlineStr"/>
     </row>
@@ -5113,13 +5128,13 @@
       <c r="T66" s="53" t="inlineStr"/>
       <c r="U66" s="53" t="inlineStr"/>
       <c r="V66" s="34" t="n"/>
-      <c r="W66" s="53" t="inlineStr"/>
-      <c r="X66" s="53" t="inlineStr"/>
-      <c r="Y66" s="53" t="inlineStr"/>
-      <c r="Z66" s="53" t="inlineStr"/>
+      <c r="W66" s="52" t="inlineStr"/>
+      <c r="X66" s="53" t="n"/>
+      <c r="Y66" s="53" t="n"/>
+      <c r="Z66" s="64" t="n"/>
       <c r="AA66" s="34" t="n"/>
       <c r="AB66" s="52" t="inlineStr"/>
-      <c r="AC66" s="34" t="n"/>
+      <c r="AC66" s="62" t="n"/>
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="55" t="inlineStr"/>
     </row>
@@ -5154,13 +5169,13 @@
       <c r="T67" s="53" t="inlineStr"/>
       <c r="U67" s="53" t="inlineStr"/>
       <c r="V67" s="34" t="n"/>
-      <c r="W67" s="53" t="inlineStr"/>
-      <c r="X67" s="53" t="inlineStr"/>
-      <c r="Y67" s="53" t="inlineStr"/>
-      <c r="Z67" s="53" t="inlineStr"/>
+      <c r="W67" s="52" t="inlineStr"/>
+      <c r="X67" s="53" t="n"/>
+      <c r="Y67" s="53" t="n"/>
+      <c r="Z67" s="64" t="n"/>
       <c r="AA67" s="34" t="n"/>
       <c r="AB67" s="52" t="inlineStr"/>
-      <c r="AC67" s="34" t="n"/>
+      <c r="AC67" s="62" t="n"/>
       <c r="AD67" s="54" t="inlineStr"/>
       <c r="AE67" s="55" t="inlineStr"/>
     </row>
@@ -5195,13 +5210,13 @@
       <c r="T68" s="53" t="inlineStr"/>
       <c r="U68" s="53" t="inlineStr"/>
       <c r="V68" s="34" t="n"/>
-      <c r="W68" s="53" t="inlineStr"/>
-      <c r="X68" s="53" t="inlineStr"/>
-      <c r="Y68" s="53" t="inlineStr"/>
-      <c r="Z68" s="53" t="inlineStr"/>
+      <c r="W68" s="52" t="inlineStr"/>
+      <c r="X68" s="53" t="n"/>
+      <c r="Y68" s="53" t="n"/>
+      <c r="Z68" s="64" t="n"/>
       <c r="AA68" s="34" t="n"/>
       <c r="AB68" s="52" t="inlineStr"/>
-      <c r="AC68" s="34" t="n"/>
+      <c r="AC68" s="62" t="n"/>
       <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="55" t="inlineStr"/>
     </row>
@@ -5210,13 +5225,13 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AE4:AE8"/>
     <mergeCell ref="AB4"/>
-    <mergeCell ref="W4:Z4"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="AD4:AD8"/>
     <mergeCell ref="A4:A8"/>
+    <mergeCell ref="W4:Y4"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="C2:F2"/>

--- a/grille_evaluation_CR.xlsx
+++ b/grille_evaluation_CR.xlsx
@@ -869,12 +869,12 @@
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Phase 1 — Pilote (membres du labo)</t>
+          <t>Phase 1 — Pilote (5 CR)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Un premier test de la grille est réalisé en interne avec les membres de l'équipe de recherche sur un petit nombre de CR. L'objectif est de vérifier la clarté des critères, d'identifier les ambiguïtés et d'ajuster la grille si nécessaire avant de la soumettre aux experts cliniques.</t>
+          <t>Un premier test de la grille et de l'outil d'évaluation est réalisé en interne avec des membres de l'équipe de recherche sur 5 comptes rendus. L'objectif est double : vérifier la clarté des critères et identifier les ambiguïtés, mais aussi tester le bon fonctionnement de l'interface d'évaluation avant de la soumettre aux experts cliniques.</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Phase 3 — Évaluation finale (60 CR)</t>
+          <t>Phase 3 — Évaluation finale (75 CR)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Chaque expert évalue 60 comptes rendus synthétiques (30 générés par Apertus-8B en 0-shot, 30 par Apertus-70B en 5-shot, température T=0,5). Un sous-ensemble de CR est évalué par les deux médecins radiothérapeutes simultanément (overlap, identifiés par * dans la grille) afin de surveiller la cohérence inter-annotateurs tout au long de l'évaluation.</t>
+          <t>Le corpus comprend 75 comptes rendus synthétiques. Chaque expert évalue 50 CR, dont 25 sont communs à plusieurs évaluateurs (overlap inter-annotateurs, identifiés par * dans la grille) afin de surveiller la cohérence inter-annotateurs tout au long de l'évaluation. Au total, l'ensemble des 75 CR sont couverts par au moins un évaluateur.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2128,8 +2128,6 @@
       </c>
       <c r="I29" s="25" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:I2"/>
